--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.17634033869182</v>
+        <v>5.55365530503742</v>
       </c>
       <c r="D2" t="n">
-        <v>25.19399763384234</v>
+        <v>4.094024615499381</v>
       </c>
       <c r="E2" t="n">
-        <v>5.578438538614694</v>
+        <v>0.9064962625248878</v>
       </c>
       <c r="F2" t="n">
-        <v>10.99845686285392</v>
+        <v>1.787249240213762</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.01010156257796</v>
+        <v>5.851641503918918</v>
       </c>
       <c r="D3" t="n">
-        <v>12.71161554959182</v>
+        <v>2.06563752680867</v>
       </c>
       <c r="E3" t="n">
-        <v>5.578438538614694</v>
+        <v>0.9064962625248878</v>
       </c>
       <c r="F3" t="n">
-        <v>10.99845686285392</v>
+        <v>1.787249240213762</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.18503911959476</v>
+        <v>3.930068856934148</v>
       </c>
       <c r="D4" t="n">
-        <v>2.217769873985541</v>
+        <v>0.3603876045226504</v>
       </c>
       <c r="E4" t="n">
-        <v>5.578438538614694</v>
+        <v>0.9064962625248878</v>
       </c>
       <c r="F4" t="n">
-        <v>10.99845686285392</v>
+        <v>1.787249240213762</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.36409483598761</v>
+        <v>3.634165410847986</v>
       </c>
       <c r="D5" t="n">
-        <v>22.13809062011796</v>
+        <v>3.597439725769169</v>
       </c>
       <c r="E5" t="n">
-        <v>5.578438538614694</v>
+        <v>0.9064962625248878</v>
       </c>
       <c r="F5" t="n">
-        <v>10.99845686285392</v>
+        <v>1.787249240213762</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.33246005964008</v>
+        <v>6.229024759691513</v>
       </c>
       <c r="D6" t="n">
-        <v>38.38785607746156</v>
+        <v>6.238026612587503</v>
       </c>
       <c r="E6" t="n">
-        <v>5.578438538614694</v>
+        <v>0.9064962625248878</v>
       </c>
       <c r="F6" t="n">
-        <v>10.99845686285392</v>
+        <v>1.787249240213762</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.67982182890414</v>
+        <v>5.147971047196923</v>
       </c>
       <c r="D7" t="n">
-        <v>30.15870174746828</v>
+        <v>4.900789033963595</v>
       </c>
       <c r="E7" t="n">
-        <v>5.578438538614694</v>
+        <v>0.9064962625248878</v>
       </c>
       <c r="F7" t="n">
-        <v>10.99845686285392</v>
+        <v>1.787249240213762</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.16934205092001</v>
+        <v>4.577518083274502</v>
       </c>
       <c r="D8" t="n">
-        <v>27.09741707351639</v>
+        <v>4.403330274446413</v>
       </c>
       <c r="E8" t="n">
-        <v>5.578438538614694</v>
+        <v>0.9064962625248878</v>
       </c>
       <c r="F8" t="n">
-        <v>10.99845686285392</v>
+        <v>1.787249240213762</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
